--- a/artfynd/A 32-2025 artfynd.xlsx
+++ b/artfynd/A 32-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>121780972</v>
       </c>
       <c r="B2" t="n">
-        <v>90783</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -781,59 +776,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121780983</v>
+        <v>121781003</v>
       </c>
       <c r="B3" t="n">
-        <v>4776</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102306</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>NO Breddrap, Ög</t>
+          <t>NO Breddarp, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>531245</v>
+        <v>531203</v>
       </c>
       <c r="R3" t="n">
-        <v>6436594</v>
+        <v>6436509</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -893,54 +877,54 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121780948</v>
+        <v>121780983</v>
       </c>
       <c r="B4" t="n">
-        <v>98159</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>4781</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>102306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>NO Breddarp, Ög</t>
+          <t>NO Breddrap, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>531298</v>
+        <v>531245</v>
       </c>
       <c r="R4" t="n">
-        <v>6436631</v>
+        <v>6436594</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1000,42 +984,38 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121781003</v>
+        <v>121780948</v>
       </c>
       <c r="B5" t="n">
-        <v>90783</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1043,10 +1023,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>531203</v>
+        <v>531298</v>
       </c>
       <c r="R5" t="n">
-        <v>6436509</v>
+        <v>6436631</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 32-2025 artfynd.xlsx
+++ b/artfynd/A 32-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121780972</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121781003</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -981,6 +996,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121780983</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1083,8 +1103,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121780948</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>